--- a/data/cleaned/dataset_maderas_final.xlsx
+++ b/data/cleaned/dataset_maderas_final.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DATA Y IA\MODULO 1\timber-supply-spanish-naval-industry\data\cleaned\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{898FB18E-4084-4115-B942-40F5D554D286}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF89E2A6-E309-413A-BDC6-EE55716C2106}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1620" yWindow="900" windowWidth="17580" windowHeight="10380" xr2:uid="{F106D049-212B-4983-914F-97B83530BB2C}"/>
+    <workbookView xWindow="1370" yWindow="900" windowWidth="17580" windowHeight="10380" xr2:uid="{F106D049-212B-4983-914F-97B83530BB2C}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4525" uniqueCount="1127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4524" uniqueCount="1126">
   <si>
     <t>felling_period</t>
   </si>
@@ -2694,9 +2694,6 @@
   </si>
   <si>
     <t>36.38279334</t>
-  </si>
-  <si>
-    <t>5.538237362</t>
   </si>
   <si>
     <t>36.6005773</t>
@@ -3811,10 +3808,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>1123</v>
+      </c>
+      <c r="C1" t="s">
         <v>1124</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1125</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>1</v>
@@ -3829,7 +3826,7 @@
         <v>4</v>
       </c>
       <c r="H1" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="I1" t="s">
         <v>5</v>
@@ -5744,20 +5741,21 @@
       <c r="D56" s="2" t="s">
         <v>884</v>
       </c>
-      <c r="E56" s="2" t="s">
-        <v>885</v>
+      <c r="E56" s="2" t="str">
+        <f>E57</f>
+        <v>-5.381514519</v>
       </c>
       <c r="F56" t="s">
-        <v>59</v>
+        <v>11</v>
       </c>
       <c r="G56" t="s">
-        <v>60</v>
+        <v>143</v>
       </c>
       <c r="H56" t="s">
         <v>13</v>
       </c>
       <c r="I56" t="s">
-        <v>60</v>
+        <v>143</v>
       </c>
       <c r="J56" t="s">
         <v>144</v>
@@ -5777,10 +5775,10 @@
         <v>158</v>
       </c>
       <c r="D57" s="2" t="s">
+        <v>885</v>
+      </c>
+      <c r="E57" s="2" t="s">
         <v>886</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>887</v>
       </c>
       <c r="F57" t="s">
         <v>59</v>
@@ -5812,10 +5810,10 @@
         <v>161</v>
       </c>
       <c r="D58" s="2" t="s">
+        <v>887</v>
+      </c>
+      <c r="E58" s="2" t="s">
         <v>888</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>889</v>
       </c>
       <c r="F58" t="s">
         <v>59</v>
@@ -5847,10 +5845,10 @@
         <v>164</v>
       </c>
       <c r="D59" s="2" t="s">
+        <v>889</v>
+      </c>
+      <c r="E59" s="2" t="s">
         <v>890</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>891</v>
       </c>
       <c r="F59" t="s">
         <v>59</v>
@@ -5882,10 +5880,10 @@
         <v>167</v>
       </c>
       <c r="D60" s="2" t="s">
+        <v>891</v>
+      </c>
+      <c r="E60" s="2" t="s">
         <v>892</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>893</v>
       </c>
       <c r="F60" t="s">
         <v>59</v>
@@ -5917,10 +5915,10 @@
         <v>170</v>
       </c>
       <c r="D61" s="2" t="s">
+        <v>893</v>
+      </c>
+      <c r="E61" s="2" t="s">
         <v>894</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>895</v>
       </c>
       <c r="F61" t="s">
         <v>59</v>
@@ -5952,10 +5950,10 @@
         <v>173</v>
       </c>
       <c r="D62" s="2" t="s">
+        <v>895</v>
+      </c>
+      <c r="E62" s="2" t="s">
         <v>896</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>897</v>
       </c>
       <c r="F62" t="s">
         <v>11</v>
@@ -5987,10 +5985,10 @@
         <v>176</v>
       </c>
       <c r="D63" s="2" t="s">
+        <v>897</v>
+      </c>
+      <c r="E63" s="2" t="s">
         <v>898</v>
-      </c>
-      <c r="E63" s="2" t="s">
-        <v>899</v>
       </c>
       <c r="F63" t="s">
         <v>11</v>
@@ -6022,10 +6020,10 @@
         <v>178</v>
       </c>
       <c r="D64" s="2" t="s">
+        <v>899</v>
+      </c>
+      <c r="E64" s="2" t="s">
         <v>900</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>901</v>
       </c>
       <c r="F64" t="s">
         <v>11</v>
@@ -6057,10 +6055,10 @@
         <v>180</v>
       </c>
       <c r="D65" s="2" t="s">
+        <v>901</v>
+      </c>
+      <c r="E65" s="2" t="s">
         <v>902</v>
-      </c>
-      <c r="E65" s="2" t="s">
-        <v>903</v>
       </c>
       <c r="F65" t="s">
         <v>11</v>
@@ -6127,10 +6125,10 @@
         <v>184</v>
       </c>
       <c r="D67" s="2" t="s">
+        <v>903</v>
+      </c>
+      <c r="E67" s="2" t="s">
         <v>904</v>
-      </c>
-      <c r="E67" s="2" t="s">
-        <v>905</v>
       </c>
       <c r="F67" t="s">
         <v>11</v>
@@ -6162,10 +6160,10 @@
         <v>187</v>
       </c>
       <c r="D68" s="2" t="s">
+        <v>905</v>
+      </c>
+      <c r="E68" s="2" t="s">
         <v>906</v>
-      </c>
-      <c r="E68" s="2" t="s">
-        <v>907</v>
       </c>
       <c r="F68" t="s">
         <v>11</v>
@@ -6197,10 +6195,10 @@
         <v>190</v>
       </c>
       <c r="D69" s="2" t="s">
+        <v>907</v>
+      </c>
+      <c r="E69" s="2" t="s">
         <v>908</v>
-      </c>
-      <c r="E69" s="2" t="s">
-        <v>909</v>
       </c>
       <c r="F69" t="s">
         <v>11</v>
@@ -6267,10 +6265,10 @@
         <v>195</v>
       </c>
       <c r="D71" s="2" t="s">
+        <v>909</v>
+      </c>
+      <c r="E71" s="2" t="s">
         <v>910</v>
-      </c>
-      <c r="E71" s="2" t="s">
-        <v>911</v>
       </c>
       <c r="F71" t="s">
         <v>11</v>
@@ -6302,10 +6300,10 @@
         <v>199</v>
       </c>
       <c r="D72" s="2" t="s">
+        <v>911</v>
+      </c>
+      <c r="E72" s="2" t="s">
         <v>912</v>
-      </c>
-      <c r="E72" s="2" t="s">
-        <v>913</v>
       </c>
       <c r="F72" t="s">
         <v>11</v>
@@ -6337,10 +6335,10 @@
         <v>201</v>
       </c>
       <c r="D73" s="2" t="s">
+        <v>913</v>
+      </c>
+      <c r="E73" s="2" t="s">
         <v>914</v>
-      </c>
-      <c r="E73" s="2" t="s">
-        <v>915</v>
       </c>
       <c r="F73" t="s">
         <v>11</v>
@@ -6372,10 +6370,10 @@
         <v>203</v>
       </c>
       <c r="D74" s="2" t="s">
+        <v>915</v>
+      </c>
+      <c r="E74" s="2" t="s">
         <v>916</v>
-      </c>
-      <c r="E74" s="2" t="s">
-        <v>917</v>
       </c>
       <c r="F74" t="s">
         <v>11</v>
@@ -6407,10 +6405,10 @@
         <v>205</v>
       </c>
       <c r="D75" s="2" t="s">
+        <v>917</v>
+      </c>
+      <c r="E75" s="2" t="s">
         <v>918</v>
-      </c>
-      <c r="E75" s="2" t="s">
-        <v>919</v>
       </c>
       <c r="F75" t="s">
         <v>11</v>
@@ -6617,10 +6615,10 @@
         <v>214</v>
       </c>
       <c r="D81" s="2" t="s">
+        <v>919</v>
+      </c>
+      <c r="E81" s="2" t="s">
         <v>920</v>
-      </c>
-      <c r="E81" s="2" t="s">
-        <v>921</v>
       </c>
       <c r="F81" t="s">
         <v>215</v>
@@ -6652,10 +6650,10 @@
         <v>219</v>
       </c>
       <c r="D82" s="2" t="s">
+        <v>921</v>
+      </c>
+      <c r="E82" s="2" t="s">
         <v>922</v>
-      </c>
-      <c r="E82" s="2" t="s">
-        <v>923</v>
       </c>
       <c r="F82" t="s">
         <v>215</v>
@@ -6687,10 +6685,10 @@
         <v>221</v>
       </c>
       <c r="D83" s="2" t="s">
+        <v>923</v>
+      </c>
+      <c r="E83" s="2" t="s">
         <v>924</v>
-      </c>
-      <c r="E83" s="2" t="s">
-        <v>925</v>
       </c>
       <c r="F83" t="s">
         <v>215</v>
@@ -6722,10 +6720,10 @@
         <v>225</v>
       </c>
       <c r="D84" s="2" t="s">
+        <v>925</v>
+      </c>
+      <c r="E84" s="2" t="s">
         <v>926</v>
-      </c>
-      <c r="E84" s="2" t="s">
-        <v>927</v>
       </c>
       <c r="F84" t="s">
         <v>215</v>
@@ -6757,10 +6755,10 @@
         <v>227</v>
       </c>
       <c r="D85" s="2" t="s">
+        <v>927</v>
+      </c>
+      <c r="E85" s="2" t="s">
         <v>928</v>
-      </c>
-      <c r="E85" s="2" t="s">
-        <v>929</v>
       </c>
       <c r="F85" t="s">
         <v>215</v>
@@ -6792,10 +6790,10 @@
         <v>232</v>
       </c>
       <c r="D86" s="2" t="s">
+        <v>929</v>
+      </c>
+      <c r="E86" s="2" t="s">
         <v>930</v>
-      </c>
-      <c r="E86" s="2" t="s">
-        <v>931</v>
       </c>
       <c r="F86" t="s">
         <v>215</v>
@@ -6827,10 +6825,10 @@
         <v>236</v>
       </c>
       <c r="D87" s="2" t="s">
+        <v>931</v>
+      </c>
+      <c r="E87" s="2" t="s">
         <v>932</v>
-      </c>
-      <c r="E87" s="2" t="s">
-        <v>933</v>
       </c>
       <c r="F87" t="s">
         <v>215</v>
@@ -6862,10 +6860,10 @@
         <v>214</v>
       </c>
       <c r="D88" s="2" t="s">
+        <v>933</v>
+      </c>
+      <c r="E88" s="2" t="s">
         <v>934</v>
-      </c>
-      <c r="E88" s="2" t="s">
-        <v>935</v>
       </c>
       <c r="F88" t="s">
         <v>215</v>
@@ -6897,10 +6895,10 @@
         <v>242</v>
       </c>
       <c r="D89" s="2" t="s">
+        <v>935</v>
+      </c>
+      <c r="E89" s="2" t="s">
         <v>936</v>
-      </c>
-      <c r="E89" s="2" t="s">
-        <v>937</v>
       </c>
       <c r="F89" t="s">
         <v>215</v>
@@ -6932,10 +6930,10 @@
         <v>246</v>
       </c>
       <c r="D90" s="2" t="s">
+        <v>937</v>
+      </c>
+      <c r="E90" s="2" t="s">
         <v>938</v>
-      </c>
-      <c r="E90" s="2" t="s">
-        <v>939</v>
       </c>
       <c r="F90" t="s">
         <v>215</v>
@@ -6967,10 +6965,10 @@
         <v>250</v>
       </c>
       <c r="D91" s="2" t="s">
+        <v>939</v>
+      </c>
+      <c r="E91" s="2" t="s">
         <v>940</v>
-      </c>
-      <c r="E91" s="2" t="s">
-        <v>941</v>
       </c>
       <c r="F91" t="s">
         <v>215</v>
@@ -7002,10 +7000,10 @@
         <v>252</v>
       </c>
       <c r="D92" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E92" s="2" t="s">
         <v>942</v>
-      </c>
-      <c r="E92" s="2" t="s">
-        <v>943</v>
       </c>
       <c r="F92" t="s">
         <v>215</v>
@@ -7037,10 +7035,10 @@
         <v>257</v>
       </c>
       <c r="D93" s="2" t="s">
+        <v>943</v>
+      </c>
+      <c r="E93" s="2" t="s">
         <v>944</v>
-      </c>
-      <c r="E93" s="2" t="s">
-        <v>945</v>
       </c>
       <c r="F93" t="s">
         <v>258</v>
@@ -7072,10 +7070,10 @@
         <v>262</v>
       </c>
       <c r="D94" s="2" t="s">
+        <v>945</v>
+      </c>
+      <c r="E94" s="2" t="s">
         <v>946</v>
-      </c>
-      <c r="E94" s="2" t="s">
-        <v>947</v>
       </c>
       <c r="F94" t="s">
         <v>258</v>
@@ -7107,10 +7105,10 @@
         <v>264</v>
       </c>
       <c r="D95" s="2" t="s">
+        <v>947</v>
+      </c>
+      <c r="E95" s="2" t="s">
         <v>948</v>
-      </c>
-      <c r="E95" s="2" t="s">
-        <v>949</v>
       </c>
       <c r="F95" t="s">
         <v>258</v>
@@ -7142,10 +7140,10 @@
         <v>269</v>
       </c>
       <c r="D96" s="2" t="s">
+        <v>949</v>
+      </c>
+      <c r="E96" s="2" t="s">
         <v>950</v>
-      </c>
-      <c r="E96" s="2" t="s">
-        <v>951</v>
       </c>
       <c r="F96" t="s">
         <v>258</v>
@@ -7212,10 +7210,10 @@
         <v>276</v>
       </c>
       <c r="D98" s="2" t="s">
+        <v>951</v>
+      </c>
+      <c r="E98" s="2" t="s">
         <v>952</v>
-      </c>
-      <c r="E98" s="2" t="s">
-        <v>953</v>
       </c>
       <c r="F98" t="s">
         <v>258</v>
@@ -7247,10 +7245,10 @@
         <v>279</v>
       </c>
       <c r="D99" s="2" t="s">
+        <v>953</v>
+      </c>
+      <c r="E99" s="2" t="s">
         <v>954</v>
-      </c>
-      <c r="E99" s="2" t="s">
-        <v>955</v>
       </c>
       <c r="F99" t="s">
         <v>258</v>
@@ -7282,10 +7280,10 @@
         <v>283</v>
       </c>
       <c r="D100" s="2" t="s">
+        <v>955</v>
+      </c>
+      <c r="E100" s="2" t="s">
         <v>956</v>
-      </c>
-      <c r="E100" s="2" t="s">
-        <v>957</v>
       </c>
       <c r="F100" t="s">
         <v>258</v>
@@ -7317,10 +7315,10 @@
         <v>287</v>
       </c>
       <c r="D101" s="2" t="s">
+        <v>957</v>
+      </c>
+      <c r="E101" s="2" t="s">
         <v>958</v>
-      </c>
-      <c r="E101" s="2" t="s">
-        <v>959</v>
       </c>
       <c r="F101" t="s">
         <v>258</v>
@@ -7352,10 +7350,10 @@
         <v>291</v>
       </c>
       <c r="D102" s="2" t="s">
+        <v>959</v>
+      </c>
+      <c r="E102" s="2" t="s">
         <v>960</v>
-      </c>
-      <c r="E102" s="2" t="s">
-        <v>961</v>
       </c>
       <c r="F102" t="s">
         <v>258</v>
@@ -7387,10 +7385,10 @@
         <v>293</v>
       </c>
       <c r="D103" s="2" t="s">
+        <v>961</v>
+      </c>
+      <c r="E103" s="2" t="s">
         <v>962</v>
-      </c>
-      <c r="E103" s="2" t="s">
-        <v>963</v>
       </c>
       <c r="F103" t="s">
         <v>258</v>
@@ -7422,10 +7420,10 @@
         <v>297</v>
       </c>
       <c r="D104" s="2" t="s">
+        <v>963</v>
+      </c>
+      <c r="E104" s="2" t="s">
         <v>964</v>
-      </c>
-      <c r="E104" s="2" t="s">
-        <v>965</v>
       </c>
       <c r="F104" t="s">
         <v>258</v>
@@ -7457,10 +7455,10 @@
         <v>302</v>
       </c>
       <c r="D105" s="2" t="s">
+        <v>965</v>
+      </c>
+      <c r="E105" s="2" t="s">
         <v>966</v>
-      </c>
-      <c r="E105" s="2" t="s">
-        <v>967</v>
       </c>
       <c r="F105" t="s">
         <v>258</v>
@@ -7492,10 +7490,10 @@
         <v>306</v>
       </c>
       <c r="D106" s="2" t="s">
+        <v>967</v>
+      </c>
+      <c r="E106" s="2" t="s">
         <v>968</v>
-      </c>
-      <c r="E106" s="2" t="s">
-        <v>969</v>
       </c>
       <c r="F106" t="s">
         <v>258</v>
@@ -7527,10 +7525,10 @@
         <v>310</v>
       </c>
       <c r="D107" s="2" t="s">
+        <v>969</v>
+      </c>
+      <c r="E107" s="2" t="s">
         <v>970</v>
-      </c>
-      <c r="E107" s="2" t="s">
-        <v>971</v>
       </c>
       <c r="F107" t="s">
         <v>258</v>
@@ -7982,10 +7980,10 @@
         <v>333</v>
       </c>
       <c r="D120" s="2" t="s">
+        <v>971</v>
+      </c>
+      <c r="E120" s="2" t="s">
         <v>972</v>
-      </c>
-      <c r="E120" s="2" t="s">
-        <v>973</v>
       </c>
       <c r="F120" t="s">
         <v>258</v>
@@ -8017,10 +8015,10 @@
         <v>337</v>
       </c>
       <c r="D121" s="2" t="s">
+        <v>973</v>
+      </c>
+      <c r="E121" s="2" t="s">
         <v>974</v>
-      </c>
-      <c r="E121" s="2" t="s">
-        <v>975</v>
       </c>
       <c r="F121" t="s">
         <v>258</v>
@@ -8052,10 +8050,10 @@
         <v>337</v>
       </c>
       <c r="D122" s="2" t="s">
+        <v>973</v>
+      </c>
+      <c r="E122" s="2" t="s">
         <v>974</v>
-      </c>
-      <c r="E122" s="2" t="s">
-        <v>975</v>
       </c>
       <c r="F122" t="s">
         <v>258</v>
@@ -8087,10 +8085,10 @@
         <v>342</v>
       </c>
       <c r="D123" s="2" t="s">
+        <v>975</v>
+      </c>
+      <c r="E123" s="2" t="s">
         <v>976</v>
-      </c>
-      <c r="E123" s="2" t="s">
-        <v>977</v>
       </c>
       <c r="F123" t="s">
         <v>258</v>
@@ -8927,10 +8925,10 @@
         <v>221</v>
       </c>
       <c r="D147" s="2" t="s">
+        <v>923</v>
+      </c>
+      <c r="E147" s="2" t="s">
         <v>924</v>
-      </c>
-      <c r="E147" s="2" t="s">
-        <v>925</v>
       </c>
       <c r="F147" t="s">
         <v>215</v>
@@ -8962,10 +8960,10 @@
         <v>382</v>
       </c>
       <c r="D148" s="2" t="s">
+        <v>977</v>
+      </c>
+      <c r="E148" s="2" t="s">
         <v>978</v>
-      </c>
-      <c r="E148" s="2" t="s">
-        <v>979</v>
       </c>
       <c r="F148" t="s">
         <v>258</v>
@@ -8997,10 +8995,10 @@
         <v>264</v>
       </c>
       <c r="D149" s="2" t="s">
+        <v>947</v>
+      </c>
+      <c r="E149" s="2" t="s">
         <v>948</v>
-      </c>
-      <c r="E149" s="2" t="s">
-        <v>949</v>
       </c>
       <c r="F149" t="s">
         <v>258</v>
@@ -9032,10 +9030,10 @@
         <v>387</v>
       </c>
       <c r="D150" s="2" t="s">
+        <v>973</v>
+      </c>
+      <c r="E150" s="2" t="s">
         <v>974</v>
-      </c>
-      <c r="E150" s="2" t="s">
-        <v>975</v>
       </c>
       <c r="F150" t="s">
         <v>258</v>
@@ -9067,10 +9065,10 @@
         <v>279</v>
       </c>
       <c r="D151" s="2" t="s">
+        <v>953</v>
+      </c>
+      <c r="E151" s="2" t="s">
         <v>954</v>
-      </c>
-      <c r="E151" s="2" t="s">
-        <v>955</v>
       </c>
       <c r="F151" t="s">
         <v>258</v>
@@ -9102,10 +9100,10 @@
         <v>283</v>
       </c>
       <c r="D152" s="2" t="s">
+        <v>955</v>
+      </c>
+      <c r="E152" s="2" t="s">
         <v>956</v>
-      </c>
-      <c r="E152" s="2" t="s">
-        <v>957</v>
       </c>
       <c r="F152" t="s">
         <v>258</v>
@@ -9137,10 +9135,10 @@
         <v>287</v>
       </c>
       <c r="D153" s="2" t="s">
+        <v>957</v>
+      </c>
+      <c r="E153" s="2" t="s">
         <v>958</v>
-      </c>
-      <c r="E153" s="2" t="s">
-        <v>959</v>
       </c>
       <c r="F153" t="s">
         <v>258</v>
@@ -9172,10 +9170,10 @@
         <v>293</v>
       </c>
       <c r="D154" s="2" t="s">
+        <v>961</v>
+      </c>
+      <c r="E154" s="2" t="s">
         <v>962</v>
-      </c>
-      <c r="E154" s="2" t="s">
-        <v>963</v>
       </c>
       <c r="F154" t="s">
         <v>258</v>
@@ -9207,10 +9205,10 @@
         <v>391</v>
       </c>
       <c r="D155" s="2" t="s">
+        <v>967</v>
+      </c>
+      <c r="E155" s="2" t="s">
         <v>968</v>
-      </c>
-      <c r="E155" s="2" t="s">
-        <v>969</v>
       </c>
       <c r="F155" t="s">
         <v>258</v>
@@ -9242,10 +9240,10 @@
         <v>393</v>
       </c>
       <c r="D156" s="2" t="s">
+        <v>969</v>
+      </c>
+      <c r="E156" s="2" t="s">
         <v>970</v>
-      </c>
-      <c r="E156" s="2" t="s">
-        <v>971</v>
       </c>
       <c r="F156" t="s">
         <v>258</v>
@@ -9277,10 +9275,10 @@
         <v>396</v>
       </c>
       <c r="D157" s="2" t="s">
+        <v>979</v>
+      </c>
+      <c r="E157" s="2" t="s">
         <v>980</v>
-      </c>
-      <c r="E157" s="2" t="s">
-        <v>981</v>
       </c>
       <c r="F157" t="s">
         <v>258</v>
@@ -9312,10 +9310,10 @@
         <v>402</v>
       </c>
       <c r="D158" s="2" t="s">
+        <v>981</v>
+      </c>
+      <c r="E158" s="2" t="s">
         <v>982</v>
-      </c>
-      <c r="E158" s="2" t="s">
-        <v>983</v>
       </c>
       <c r="F158" t="s">
         <v>258</v>
@@ -9347,10 +9345,10 @@
         <v>406</v>
       </c>
       <c r="D159" s="2" t="s">
+        <v>983</v>
+      </c>
+      <c r="E159" s="2" t="s">
         <v>984</v>
-      </c>
-      <c r="E159" s="2" t="s">
-        <v>985</v>
       </c>
       <c r="F159" t="s">
         <v>258</v>
@@ -9382,10 +9380,10 @@
         <v>409</v>
       </c>
       <c r="D160" s="2" t="s">
+        <v>985</v>
+      </c>
+      <c r="E160" s="2" t="s">
         <v>986</v>
-      </c>
-      <c r="E160" s="2" t="s">
-        <v>987</v>
       </c>
       <c r="F160" t="s">
         <v>258</v>
@@ -9417,10 +9415,10 @@
         <v>412</v>
       </c>
       <c r="D161" s="2" t="s">
+        <v>987</v>
+      </c>
+      <c r="E161" s="2" t="s">
         <v>988</v>
-      </c>
-      <c r="E161" s="2" t="s">
-        <v>989</v>
       </c>
       <c r="F161" t="s">
         <v>258</v>
@@ -9452,10 +9450,10 @@
         <v>414</v>
       </c>
       <c r="D162" s="2" t="s">
+        <v>989</v>
+      </c>
+      <c r="E162" s="2" t="s">
         <v>990</v>
-      </c>
-      <c r="E162" s="2" t="s">
-        <v>991</v>
       </c>
       <c r="F162" t="s">
         <v>258</v>
@@ -9487,10 +9485,10 @@
         <v>416</v>
       </c>
       <c r="D163" s="2" t="s">
+        <v>991</v>
+      </c>
+      <c r="E163" s="2" t="s">
         <v>992</v>
-      </c>
-      <c r="E163" s="2" t="s">
-        <v>993</v>
       </c>
       <c r="F163" t="s">
         <v>258</v>
@@ -9522,10 +9520,10 @@
         <v>419</v>
       </c>
       <c r="D164" s="2" t="s">
+        <v>993</v>
+      </c>
+      <c r="E164" s="2" t="s">
         <v>994</v>
-      </c>
-      <c r="E164" s="2" t="s">
-        <v>995</v>
       </c>
       <c r="F164" t="s">
         <v>258</v>
@@ -9557,10 +9555,10 @@
         <v>422</v>
       </c>
       <c r="D165" s="2" t="s">
+        <v>995</v>
+      </c>
+      <c r="E165" s="2" t="s">
         <v>996</v>
-      </c>
-      <c r="E165" s="2" t="s">
-        <v>997</v>
       </c>
       <c r="F165" t="s">
         <v>258</v>
@@ -9592,10 +9590,10 @@
         <v>424</v>
       </c>
       <c r="D166" s="2" t="s">
+        <v>997</v>
+      </c>
+      <c r="E166" s="2" t="s">
         <v>998</v>
-      </c>
-      <c r="E166" s="2" t="s">
-        <v>999</v>
       </c>
       <c r="F166" t="s">
         <v>258</v>
@@ -9627,10 +9625,10 @@
         <v>427</v>
       </c>
       <c r="D167" s="2" t="s">
+        <v>999</v>
+      </c>
+      <c r="E167" s="2" t="s">
         <v>1000</v>
-      </c>
-      <c r="E167" s="2" t="s">
-        <v>1001</v>
       </c>
       <c r="F167" t="s">
         <v>258</v>
@@ -9662,10 +9660,10 @@
         <v>428</v>
       </c>
       <c r="D168" s="2" t="s">
+        <v>1001</v>
+      </c>
+      <c r="E168" s="2" t="s">
         <v>1002</v>
-      </c>
-      <c r="E168" s="2" t="s">
-        <v>1003</v>
       </c>
       <c r="F168" t="s">
         <v>258</v>
@@ -9697,10 +9695,10 @@
         <v>430</v>
       </c>
       <c r="D169" s="2" t="s">
+        <v>1003</v>
+      </c>
+      <c r="E169" s="2" t="s">
         <v>1004</v>
-      </c>
-      <c r="E169" s="2" t="s">
-        <v>1005</v>
       </c>
       <c r="F169" t="s">
         <v>258</v>
@@ -9732,10 +9730,10 @@
         <v>432</v>
       </c>
       <c r="D170" s="2" t="s">
+        <v>1005</v>
+      </c>
+      <c r="E170" s="2" t="s">
         <v>1006</v>
-      </c>
-      <c r="E170" s="2" t="s">
-        <v>1007</v>
       </c>
       <c r="F170" t="s">
         <v>258</v>
@@ -9767,10 +9765,10 @@
         <v>434</v>
       </c>
       <c r="D171" s="2" t="s">
+        <v>1007</v>
+      </c>
+      <c r="E171" s="2" t="s">
         <v>1008</v>
-      </c>
-      <c r="E171" s="2" t="s">
-        <v>1009</v>
       </c>
       <c r="F171" t="s">
         <v>258</v>
@@ -9802,10 +9800,10 @@
         <v>438</v>
       </c>
       <c r="D172" s="2" t="s">
+        <v>1009</v>
+      </c>
+      <c r="E172" s="2" t="s">
         <v>1010</v>
-      </c>
-      <c r="E172" s="2" t="s">
-        <v>1011</v>
       </c>
       <c r="F172" t="s">
         <v>258</v>
@@ -9837,10 +9835,10 @@
         <v>220</v>
       </c>
       <c r="D173" s="2" t="s">
+        <v>923</v>
+      </c>
+      <c r="E173" s="2" t="s">
         <v>924</v>
-      </c>
-      <c r="E173" s="2" t="s">
-        <v>925</v>
       </c>
       <c r="F173" t="s">
         <v>215</v>
@@ -9872,10 +9870,10 @@
         <v>443</v>
       </c>
       <c r="D174" s="2" t="s">
+        <v>929</v>
+      </c>
+      <c r="E174" s="2" t="s">
         <v>930</v>
-      </c>
-      <c r="E174" s="2" t="s">
-        <v>931</v>
       </c>
       <c r="F174" t="s">
         <v>215</v>
@@ -9907,10 +9905,10 @@
         <v>443</v>
       </c>
       <c r="D175" s="2" t="s">
+        <v>929</v>
+      </c>
+      <c r="E175" s="2" t="s">
         <v>930</v>
-      </c>
-      <c r="E175" s="2" t="s">
-        <v>931</v>
       </c>
       <c r="F175" t="s">
         <v>215</v>
@@ -9942,10 +9940,10 @@
         <v>236</v>
       </c>
       <c r="D176" s="2" t="s">
+        <v>931</v>
+      </c>
+      <c r="E176" s="2" t="s">
         <v>932</v>
-      </c>
-      <c r="E176" s="2" t="s">
-        <v>933</v>
       </c>
       <c r="F176" t="s">
         <v>215</v>
@@ -9977,10 +9975,10 @@
         <v>246</v>
       </c>
       <c r="D177" s="2" t="s">
+        <v>937</v>
+      </c>
+      <c r="E177" s="2" t="s">
         <v>938</v>
-      </c>
-      <c r="E177" s="2" t="s">
-        <v>939</v>
       </c>
       <c r="F177" t="s">
         <v>215</v>
@@ -10012,10 +10010,10 @@
         <v>242</v>
       </c>
       <c r="D178" s="2" t="s">
+        <v>935</v>
+      </c>
+      <c r="E178" s="2" t="s">
         <v>936</v>
-      </c>
-      <c r="E178" s="2" t="s">
-        <v>937</v>
       </c>
       <c r="F178" t="s">
         <v>215</v>
@@ -10047,10 +10045,10 @@
         <v>283</v>
       </c>
       <c r="D179" s="2" t="s">
+        <v>955</v>
+      </c>
+      <c r="E179" s="2" t="s">
         <v>956</v>
-      </c>
-      <c r="E179" s="2" t="s">
-        <v>957</v>
       </c>
       <c r="F179" t="s">
         <v>258</v>
@@ -10187,10 +10185,10 @@
         <v>456</v>
       </c>
       <c r="D183" s="2" t="s">
+        <v>1011</v>
+      </c>
+      <c r="E183" s="2" t="s">
         <v>1012</v>
-      </c>
-      <c r="E183" s="2" t="s">
-        <v>1013</v>
       </c>
       <c r="F183" t="s">
         <v>258</v>
@@ -10222,10 +10220,10 @@
         <v>214</v>
       </c>
       <c r="D184" s="2" t="s">
+        <v>1013</v>
+      </c>
+      <c r="E184" s="2" t="s">
         <v>1014</v>
-      </c>
-      <c r="E184" s="2" t="s">
-        <v>1015</v>
       </c>
       <c r="F184" t="s">
         <v>215</v>
@@ -10257,10 +10255,10 @@
         <v>462</v>
       </c>
       <c r="D185" s="2" t="s">
+        <v>1015</v>
+      </c>
+      <c r="E185" s="2" t="s">
         <v>1016</v>
-      </c>
-      <c r="E185" s="2" t="s">
-        <v>1017</v>
       </c>
       <c r="F185" t="s">
         <v>215</v>
@@ -10292,10 +10290,10 @@
         <v>466</v>
       </c>
       <c r="D186" s="2" t="s">
+        <v>1017</v>
+      </c>
+      <c r="E186" s="2" t="s">
         <v>1018</v>
-      </c>
-      <c r="E186" s="2" t="s">
-        <v>1019</v>
       </c>
       <c r="F186" t="s">
         <v>215</v>
@@ -10327,10 +10325,10 @@
         <v>214</v>
       </c>
       <c r="D187" s="2" t="s">
+        <v>1019</v>
+      </c>
+      <c r="E187" s="2" t="s">
         <v>1020</v>
-      </c>
-      <c r="E187" s="2" t="s">
-        <v>1021</v>
       </c>
       <c r="F187" t="s">
         <v>215</v>
@@ -10362,10 +10360,10 @@
         <v>473</v>
       </c>
       <c r="D188" s="2" t="s">
+        <v>1021</v>
+      </c>
+      <c r="E188" s="2" t="s">
         <v>1022</v>
-      </c>
-      <c r="E188" s="2" t="s">
-        <v>1023</v>
       </c>
       <c r="F188" t="s">
         <v>215</v>
@@ -10432,10 +10430,10 @@
         <v>225</v>
       </c>
       <c r="D190" s="2" t="s">
+        <v>925</v>
+      </c>
+      <c r="E190" s="2" t="s">
         <v>926</v>
-      </c>
-      <c r="E190" s="2" t="s">
-        <v>927</v>
       </c>
       <c r="F190" t="s">
         <v>215</v>
@@ -10467,10 +10465,10 @@
         <v>481</v>
       </c>
       <c r="D191" s="2" t="s">
+        <v>1023</v>
+      </c>
+      <c r="E191" s="2" t="s">
         <v>1024</v>
-      </c>
-      <c r="E191" s="2" t="s">
-        <v>1025</v>
       </c>
       <c r="F191" t="s">
         <v>215</v>
@@ -10502,10 +10500,10 @@
         <v>227</v>
       </c>
       <c r="D192" s="2" t="s">
+        <v>927</v>
+      </c>
+      <c r="E192" s="2" t="s">
         <v>928</v>
-      </c>
-      <c r="E192" s="2" t="s">
-        <v>929</v>
       </c>
       <c r="F192" t="s">
         <v>215</v>
@@ -10537,10 +10535,10 @@
         <v>485</v>
       </c>
       <c r="D193" s="2" t="s">
+        <v>1025</v>
+      </c>
+      <c r="E193" s="2" t="s">
         <v>1026</v>
-      </c>
-      <c r="E193" s="2" t="s">
-        <v>1027</v>
       </c>
       <c r="F193" t="s">
         <v>215</v>
@@ -10572,10 +10570,10 @@
         <v>242</v>
       </c>
       <c r="D194" s="2" t="s">
+        <v>935</v>
+      </c>
+      <c r="E194" s="2" t="s">
         <v>936</v>
-      </c>
-      <c r="E194" s="2" t="s">
-        <v>937</v>
       </c>
       <c r="F194" t="s">
         <v>215</v>
@@ -10607,10 +10605,10 @@
         <v>246</v>
       </c>
       <c r="D195" s="2" t="s">
+        <v>937</v>
+      </c>
+      <c r="E195" s="2" t="s">
         <v>938</v>
-      </c>
-      <c r="E195" s="2" t="s">
-        <v>939</v>
       </c>
       <c r="F195" t="s">
         <v>215</v>
@@ -10642,10 +10640,10 @@
         <v>488</v>
       </c>
       <c r="D196" s="2" t="s">
+        <v>1027</v>
+      </c>
+      <c r="E196" s="2" t="s">
         <v>1028</v>
-      </c>
-      <c r="E196" s="2" t="s">
-        <v>1029</v>
       </c>
       <c r="F196" t="s">
         <v>215</v>
@@ -10677,10 +10675,10 @@
         <v>74</v>
       </c>
       <c r="D197" s="2" t="s">
+        <v>1029</v>
+      </c>
+      <c r="E197" s="2" t="s">
         <v>1030</v>
-      </c>
-      <c r="E197" s="2" t="s">
-        <v>1031</v>
       </c>
       <c r="F197" t="s">
         <v>215</v>
@@ -10747,10 +10745,10 @@
         <v>494</v>
       </c>
       <c r="D199" s="2" t="s">
+        <v>1031</v>
+      </c>
+      <c r="E199" s="2" t="s">
         <v>1032</v>
-      </c>
-      <c r="E199" s="2" t="s">
-        <v>1033</v>
       </c>
       <c r="F199" t="s">
         <v>215</v>
@@ -10782,10 +10780,10 @@
         <v>494</v>
       </c>
       <c r="D200" s="2" t="s">
+        <v>1031</v>
+      </c>
+      <c r="E200" s="2" t="s">
         <v>1032</v>
-      </c>
-      <c r="E200" s="2" t="s">
-        <v>1033</v>
       </c>
       <c r="F200" t="s">
         <v>215</v>
@@ -10817,10 +10815,10 @@
         <v>498</v>
       </c>
       <c r="D201" s="2" t="s">
+        <v>1033</v>
+      </c>
+      <c r="E201" s="2" t="s">
         <v>1034</v>
-      </c>
-      <c r="E201" s="2" t="s">
-        <v>1035</v>
       </c>
       <c r="F201" t="s">
         <v>215</v>
@@ -10852,10 +10850,10 @@
         <v>502</v>
       </c>
       <c r="D202" s="2" t="s">
+        <v>1035</v>
+      </c>
+      <c r="E202" s="2" t="s">
         <v>1036</v>
-      </c>
-      <c r="E202" s="2" t="s">
-        <v>1037</v>
       </c>
       <c r="F202" t="s">
         <v>215</v>
@@ -10887,10 +10885,10 @@
         <v>503</v>
       </c>
       <c r="D203" s="2" t="s">
+        <v>939</v>
+      </c>
+      <c r="E203" s="2" t="s">
         <v>940</v>
-      </c>
-      <c r="E203" s="2" t="s">
-        <v>941</v>
       </c>
       <c r="F203" t="s">
         <v>215</v>
@@ -10922,10 +10920,10 @@
         <v>505</v>
       </c>
       <c r="D204" s="2" t="s">
+        <v>1037</v>
+      </c>
+      <c r="E204" s="2" t="s">
         <v>1038</v>
-      </c>
-      <c r="E204" s="2" t="s">
-        <v>1039</v>
       </c>
       <c r="F204" t="s">
         <v>215</v>
@@ -10957,10 +10955,10 @@
         <v>507</v>
       </c>
       <c r="D205" s="2" t="s">
+        <v>1039</v>
+      </c>
+      <c r="E205" s="2" t="s">
         <v>1040</v>
-      </c>
-      <c r="E205" s="2" t="s">
-        <v>1041</v>
       </c>
       <c r="F205" t="s">
         <v>215</v>
@@ -10992,10 +10990,10 @@
         <v>511</v>
       </c>
       <c r="D206" s="2" t="s">
+        <v>1041</v>
+      </c>
+      <c r="E206" s="2" t="s">
         <v>1042</v>
-      </c>
-      <c r="E206" s="2" t="s">
-        <v>1043</v>
       </c>
       <c r="F206" t="s">
         <v>215</v>
@@ -11027,10 +11025,10 @@
         <v>252</v>
       </c>
       <c r="D207" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E207" s="2" t="s">
         <v>942</v>
-      </c>
-      <c r="E207" s="2" t="s">
-        <v>943</v>
       </c>
       <c r="F207" t="s">
         <v>215</v>
@@ -11062,10 +11060,10 @@
         <v>214</v>
       </c>
       <c r="D208" s="2" t="s">
+        <v>1043</v>
+      </c>
+      <c r="E208" s="2" t="s">
         <v>1044</v>
-      </c>
-      <c r="E208" s="2" t="s">
-        <v>1045</v>
       </c>
       <c r="F208" t="s">
         <v>215</v>
@@ -11097,10 +11095,10 @@
         <v>519</v>
       </c>
       <c r="D209" s="2" t="s">
+        <v>1045</v>
+      </c>
+      <c r="E209" s="2" t="s">
         <v>1046</v>
-      </c>
-      <c r="E209" s="2" t="s">
-        <v>1047</v>
       </c>
       <c r="F209" t="s">
         <v>215</v>
@@ -11132,10 +11130,10 @@
         <v>522</v>
       </c>
       <c r="D210" s="2" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E210" s="2" t="s">
         <v>1048</v>
-      </c>
-      <c r="E210" s="2" t="s">
-        <v>1049</v>
       </c>
       <c r="F210" t="s">
         <v>215</v>
@@ -11167,10 +11165,10 @@
         <v>525</v>
       </c>
       <c r="D211" s="2" t="s">
+        <v>1049</v>
+      </c>
+      <c r="E211" s="2" t="s">
         <v>1050</v>
-      </c>
-      <c r="E211" s="2" t="s">
-        <v>1051</v>
       </c>
       <c r="F211" t="s">
         <v>215</v>
@@ -11202,10 +11200,10 @@
         <v>529</v>
       </c>
       <c r="D212" s="2" t="s">
+        <v>1051</v>
+      </c>
+      <c r="E212" s="2" t="s">
         <v>1052</v>
-      </c>
-      <c r="E212" s="2" t="s">
-        <v>1053</v>
       </c>
       <c r="F212" t="s">
         <v>215</v>
@@ -11237,10 +11235,10 @@
         <v>532</v>
       </c>
       <c r="D213" s="2" t="s">
+        <v>1053</v>
+      </c>
+      <c r="E213" s="2" t="s">
         <v>1054</v>
-      </c>
-      <c r="E213" s="2" t="s">
-        <v>1055</v>
       </c>
       <c r="F213" t="s">
         <v>215</v>
@@ -11342,10 +11340,10 @@
         <v>539</v>
       </c>
       <c r="D216" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="E216" s="2" t="s">
         <v>1056</v>
-      </c>
-      <c r="E216" s="2" t="s">
-        <v>1057</v>
       </c>
       <c r="F216" t="s">
         <v>215</v>
@@ -11377,10 +11375,10 @@
         <v>543</v>
       </c>
       <c r="D217" s="2" t="s">
+        <v>1057</v>
+      </c>
+      <c r="E217" s="2" t="s">
         <v>1058</v>
-      </c>
-      <c r="E217" s="2" t="s">
-        <v>1059</v>
       </c>
       <c r="F217" t="s">
         <v>215</v>
@@ -11412,10 +11410,10 @@
         <v>333</v>
       </c>
       <c r="D218" s="2" t="s">
+        <v>971</v>
+      </c>
+      <c r="E218" s="2" t="s">
         <v>972</v>
-      </c>
-      <c r="E218" s="2" t="s">
-        <v>973</v>
       </c>
       <c r="F218" t="s">
         <v>258</v>
@@ -11447,10 +11445,10 @@
         <v>276</v>
       </c>
       <c r="D219" s="2" t="s">
+        <v>951</v>
+      </c>
+      <c r="E219" s="2" t="s">
         <v>952</v>
-      </c>
-      <c r="E219" s="2" t="s">
-        <v>953</v>
       </c>
       <c r="F219" t="s">
         <v>258</v>
@@ -11482,10 +11480,10 @@
         <v>283</v>
       </c>
       <c r="D220" s="2" t="s">
+        <v>955</v>
+      </c>
+      <c r="E220" s="2" t="s">
         <v>956</v>
-      </c>
-      <c r="E220" s="2" t="s">
-        <v>957</v>
       </c>
       <c r="F220" t="s">
         <v>258</v>
@@ -11517,10 +11515,10 @@
         <v>279</v>
       </c>
       <c r="D221" s="2" t="s">
+        <v>953</v>
+      </c>
+      <c r="E221" s="2" t="s">
         <v>954</v>
-      </c>
-      <c r="E221" s="2" t="s">
-        <v>955</v>
       </c>
       <c r="F221" t="s">
         <v>258</v>
@@ -11552,10 +11550,10 @@
         <v>287</v>
       </c>
       <c r="D222" s="2" t="s">
+        <v>957</v>
+      </c>
+      <c r="E222" s="2" t="s">
         <v>958</v>
-      </c>
-      <c r="E222" s="2" t="s">
-        <v>959</v>
       </c>
       <c r="F222" t="s">
         <v>258</v>
@@ -11587,10 +11585,10 @@
         <v>296</v>
       </c>
       <c r="D223" s="2" t="s">
+        <v>963</v>
+      </c>
+      <c r="E223" s="2" t="s">
         <v>964</v>
-      </c>
-      <c r="E223" s="2" t="s">
-        <v>965</v>
       </c>
       <c r="F223" t="s">
         <v>258</v>
@@ -11622,10 +11620,10 @@
         <v>547</v>
       </c>
       <c r="D224" s="2" t="s">
+        <v>1059</v>
+      </c>
+      <c r="E224" s="2" t="s">
         <v>1060</v>
-      </c>
-      <c r="E224" s="2" t="s">
-        <v>1061</v>
       </c>
       <c r="F224" t="s">
         <v>258</v>
@@ -11657,10 +11655,10 @@
         <v>549</v>
       </c>
       <c r="D225" s="2" t="s">
+        <v>1061</v>
+      </c>
+      <c r="E225" s="2" t="s">
         <v>1062</v>
-      </c>
-      <c r="E225" s="2" t="s">
-        <v>1063</v>
       </c>
       <c r="F225" t="s">
         <v>258</v>
@@ -11692,10 +11690,10 @@
         <v>551</v>
       </c>
       <c r="D226" s="2" t="s">
+        <v>1063</v>
+      </c>
+      <c r="E226" s="2" t="s">
         <v>1064</v>
-      </c>
-      <c r="E226" s="2" t="s">
-        <v>1065</v>
       </c>
       <c r="F226" t="s">
         <v>258</v>
@@ -11727,10 +11725,10 @@
         <v>551</v>
       </c>
       <c r="D227" s="2" t="s">
+        <v>1063</v>
+      </c>
+      <c r="E227" s="2" t="s">
         <v>1064</v>
-      </c>
-      <c r="E227" s="2" t="s">
-        <v>1065</v>
       </c>
       <c r="F227" t="s">
         <v>258</v>
@@ -11832,10 +11830,10 @@
         <v>559</v>
       </c>
       <c r="D230" s="2" t="s">
+        <v>1065</v>
+      </c>
+      <c r="E230" s="2" t="s">
         <v>1066</v>
-      </c>
-      <c r="E230" s="2" t="s">
-        <v>1067</v>
       </c>
       <c r="F230" t="s">
         <v>258</v>
@@ -11867,10 +11865,10 @@
         <v>562</v>
       </c>
       <c r="D231" s="2" t="s">
+        <v>1067</v>
+      </c>
+      <c r="E231" s="2" t="s">
         <v>1068</v>
-      </c>
-      <c r="E231" s="2" t="s">
-        <v>1069</v>
       </c>
       <c r="F231" t="s">
         <v>258</v>
@@ -11937,10 +11935,10 @@
         <v>566</v>
       </c>
       <c r="D233" s="2" t="s">
+        <v>1069</v>
+      </c>
+      <c r="E233" s="2" t="s">
         <v>1070</v>
-      </c>
-      <c r="E233" s="2" t="s">
-        <v>1071</v>
       </c>
       <c r="F233" t="s">
         <v>258</v>
@@ -11972,10 +11970,10 @@
         <v>569</v>
       </c>
       <c r="D234" s="2" t="s">
+        <v>1071</v>
+      </c>
+      <c r="E234" s="2" t="s">
         <v>1072</v>
-      </c>
-      <c r="E234" s="2" t="s">
-        <v>1073</v>
       </c>
       <c r="F234" t="s">
         <v>258</v>
@@ -12007,10 +12005,10 @@
         <v>569</v>
       </c>
       <c r="D235" s="2" t="s">
+        <v>1071</v>
+      </c>
+      <c r="E235" s="2" t="s">
         <v>1072</v>
-      </c>
-      <c r="E235" s="2" t="s">
-        <v>1073</v>
       </c>
       <c r="F235" t="s">
         <v>258</v>
@@ -12042,10 +12040,10 @@
         <v>573</v>
       </c>
       <c r="D236" s="2" t="s">
+        <v>1073</v>
+      </c>
+      <c r="E236" s="2" t="s">
         <v>1074</v>
-      </c>
-      <c r="E236" s="2" t="s">
-        <v>1075</v>
       </c>
       <c r="F236" t="s">
         <v>258</v>
@@ -12077,10 +12075,10 @@
         <v>575</v>
       </c>
       <c r="D237" s="2" t="s">
+        <v>1075</v>
+      </c>
+      <c r="E237" s="2" t="s">
         <v>1076</v>
-      </c>
-      <c r="E237" s="2" t="s">
-        <v>1077</v>
       </c>
       <c r="F237" t="s">
         <v>258</v>
@@ -12112,10 +12110,10 @@
         <v>578</v>
       </c>
       <c r="D238" s="2" t="s">
+        <v>1077</v>
+      </c>
+      <c r="E238" s="2" t="s">
         <v>1078</v>
-      </c>
-      <c r="E238" s="2" t="s">
-        <v>1079</v>
       </c>
       <c r="F238" t="s">
         <v>258</v>
@@ -12147,10 +12145,10 @@
         <v>578</v>
       </c>
       <c r="D239" s="2" t="s">
+        <v>1077</v>
+      </c>
+      <c r="E239" s="2" t="s">
         <v>1078</v>
-      </c>
-      <c r="E239" s="2" t="s">
-        <v>1079</v>
       </c>
       <c r="F239" t="s">
         <v>258</v>
@@ -12182,10 +12180,10 @@
         <v>581</v>
       </c>
       <c r="D240" s="2" t="s">
+        <v>1079</v>
+      </c>
+      <c r="E240" s="2" t="s">
         <v>1080</v>
-      </c>
-      <c r="E240" s="2" t="s">
-        <v>1081</v>
       </c>
       <c r="F240" t="s">
         <v>258</v>
@@ -12217,10 +12215,10 @@
         <v>584</v>
       </c>
       <c r="D241" s="2" t="s">
+        <v>1081</v>
+      </c>
+      <c r="E241" s="2" t="s">
         <v>1082</v>
-      </c>
-      <c r="E241" s="2" t="s">
-        <v>1083</v>
       </c>
       <c r="F241" t="s">
         <v>258</v>
@@ -12322,10 +12320,10 @@
         <v>590</v>
       </c>
       <c r="D244" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="E244" s="2" t="s">
         <v>1084</v>
-      </c>
-      <c r="E244" s="2" t="s">
-        <v>1085</v>
       </c>
       <c r="F244" t="s">
         <v>258</v>
@@ -12357,10 +12355,10 @@
         <v>592</v>
       </c>
       <c r="D245" s="2" t="s">
+        <v>1011</v>
+      </c>
+      <c r="E245" s="2" t="s">
         <v>1012</v>
-      </c>
-      <c r="E245" s="2" t="s">
-        <v>1013</v>
       </c>
       <c r="F245" t="s">
         <v>258</v>
@@ -12392,10 +12390,10 @@
         <v>594</v>
       </c>
       <c r="D246" s="2" t="s">
+        <v>1085</v>
+      </c>
+      <c r="E246" s="2" t="s">
         <v>1086</v>
-      </c>
-      <c r="E246" s="2" t="s">
-        <v>1087</v>
       </c>
       <c r="F246" t="s">
         <v>258</v>
@@ -12567,10 +12565,10 @@
         <v>603</v>
       </c>
       <c r="D251" s="2" t="s">
+        <v>1087</v>
+      </c>
+      <c r="E251" s="2" t="s">
         <v>1088</v>
-      </c>
-      <c r="E251" s="2" t="s">
-        <v>1089</v>
       </c>
       <c r="F251" t="s">
         <v>258</v>
@@ -12602,10 +12600,10 @@
         <v>604</v>
       </c>
       <c r="D252" s="2" t="s">
+        <v>1089</v>
+      </c>
+      <c r="E252" s="2" t="s">
         <v>1090</v>
-      </c>
-      <c r="E252" s="2" t="s">
-        <v>1091</v>
       </c>
       <c r="F252" t="s">
         <v>258</v>
@@ -12637,10 +12635,10 @@
         <v>606</v>
       </c>
       <c r="D253" s="2" t="s">
+        <v>1091</v>
+      </c>
+      <c r="E253" s="2" t="s">
         <v>1092</v>
-      </c>
-      <c r="E253" s="2" t="s">
-        <v>1093</v>
       </c>
       <c r="F253" t="s">
         <v>258</v>
@@ -12672,10 +12670,10 @@
         <v>608</v>
       </c>
       <c r="D254" s="2" t="s">
+        <v>1093</v>
+      </c>
+      <c r="E254" s="2" t="s">
         <v>1094</v>
-      </c>
-      <c r="E254" s="2" t="s">
-        <v>1095</v>
       </c>
       <c r="F254" t="s">
         <v>258</v>
@@ -14317,10 +14315,10 @@
         <v>662</v>
       </c>
       <c r="D301" s="2" t="s">
+        <v>949</v>
+      </c>
+      <c r="E301" s="2" t="s">
         <v>950</v>
-      </c>
-      <c r="E301" s="2" t="s">
-        <v>951</v>
       </c>
       <c r="F301" t="s">
         <v>215</v>
@@ -14352,10 +14350,10 @@
         <v>666</v>
       </c>
       <c r="D302" s="2" t="s">
+        <v>1095</v>
+      </c>
+      <c r="E302" s="2" t="s">
         <v>1096</v>
-      </c>
-      <c r="E302" s="2" t="s">
-        <v>1097</v>
       </c>
       <c r="F302" t="s">
         <v>215</v>
@@ -17082,10 +17080,10 @@
         <v>747</v>
       </c>
       <c r="D380" s="2" t="s">
+        <v>1097</v>
+      </c>
+      <c r="E380" s="2" t="s">
         <v>1098</v>
-      </c>
-      <c r="E380" s="2" t="s">
-        <v>1099</v>
       </c>
       <c r="F380" t="s">
         <v>258</v>
@@ -17187,10 +17185,10 @@
         <v>214</v>
       </c>
       <c r="D383" s="2" t="s">
+        <v>1019</v>
+      </c>
+      <c r="E383" s="2" t="s">
         <v>1020</v>
-      </c>
-      <c r="E383" s="2" t="s">
-        <v>1021</v>
       </c>
       <c r="F383" t="s">
         <v>215</v>
@@ -17222,10 +17220,10 @@
         <v>214</v>
       </c>
       <c r="D384" s="2" t="s">
+        <v>1013</v>
+      </c>
+      <c r="E384" s="2" t="s">
         <v>1014</v>
-      </c>
-      <c r="E384" s="2" t="s">
-        <v>1015</v>
       </c>
       <c r="F384" t="s">
         <v>215</v>
@@ -17257,10 +17255,10 @@
         <v>750</v>
       </c>
       <c r="D385" s="2" t="s">
+        <v>1099</v>
+      </c>
+      <c r="E385" s="2" t="s">
         <v>1100</v>
-      </c>
-      <c r="E385" s="2" t="s">
-        <v>1101</v>
       </c>
       <c r="F385" t="s">
         <v>258</v>
@@ -17292,10 +17290,10 @@
         <v>221</v>
       </c>
       <c r="D386" s="2" t="s">
+        <v>923</v>
+      </c>
+      <c r="E386" s="2" t="s">
         <v>924</v>
-      </c>
-      <c r="E386" s="2" t="s">
-        <v>925</v>
       </c>
       <c r="F386" t="s">
         <v>215</v>
@@ -17327,10 +17325,10 @@
         <v>225</v>
       </c>
       <c r="D387" s="2" t="s">
+        <v>925</v>
+      </c>
+      <c r="E387" s="2" t="s">
         <v>926</v>
-      </c>
-      <c r="E387" s="2" t="s">
-        <v>927</v>
       </c>
       <c r="F387" t="s">
         <v>215</v>
@@ -17362,10 +17360,10 @@
         <v>227</v>
       </c>
       <c r="D388" s="2" t="s">
+        <v>927</v>
+      </c>
+      <c r="E388" s="2" t="s">
         <v>928</v>
-      </c>
-      <c r="E388" s="2" t="s">
-        <v>929</v>
       </c>
       <c r="F388" t="s">
         <v>215</v>
@@ -17397,10 +17395,10 @@
         <v>242</v>
       </c>
       <c r="D389" s="2" t="s">
+        <v>935</v>
+      </c>
+      <c r="E389" s="2" t="s">
         <v>936</v>
-      </c>
-      <c r="E389" s="2" t="s">
-        <v>937</v>
       </c>
       <c r="F389" t="s">
         <v>215</v>
@@ -17432,10 +17430,10 @@
         <v>246</v>
       </c>
       <c r="D390" s="2" t="s">
+        <v>937</v>
+      </c>
+      <c r="E390" s="2" t="s">
         <v>938</v>
-      </c>
-      <c r="E390" s="2" t="s">
-        <v>939</v>
       </c>
       <c r="F390" t="s">
         <v>215</v>
@@ -17642,10 +17640,10 @@
         <v>766</v>
       </c>
       <c r="D396" s="2" t="s">
+        <v>1101</v>
+      </c>
+      <c r="E396" s="2" t="s">
         <v>1102</v>
-      </c>
-      <c r="E396" s="2" t="s">
-        <v>1103</v>
       </c>
       <c r="F396" t="s">
         <v>215</v>
@@ -17677,10 +17675,10 @@
         <v>768</v>
       </c>
       <c r="D397" s="2" t="s">
+        <v>1103</v>
+      </c>
+      <c r="E397" s="2" t="s">
         <v>1104</v>
-      </c>
-      <c r="E397" s="2" t="s">
-        <v>1105</v>
       </c>
       <c r="F397" t="s">
         <v>215</v>
@@ -17712,10 +17710,10 @@
         <v>770</v>
       </c>
       <c r="D398" s="2" t="s">
+        <v>1105</v>
+      </c>
+      <c r="E398" s="2" t="s">
         <v>1106</v>
-      </c>
-      <c r="E398" s="2" t="s">
-        <v>1107</v>
       </c>
       <c r="F398" t="s">
         <v>215</v>
@@ -17747,10 +17745,10 @@
         <v>539</v>
       </c>
       <c r="D399" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="E399" s="2" t="s">
         <v>1056</v>
-      </c>
-      <c r="E399" s="2" t="s">
-        <v>1057</v>
       </c>
       <c r="F399" t="s">
         <v>215</v>
@@ -17782,10 +17780,10 @@
         <v>773</v>
       </c>
       <c r="D400" s="2" t="s">
+        <v>1107</v>
+      </c>
+      <c r="E400" s="2" t="s">
         <v>1108</v>
-      </c>
-      <c r="E400" s="2" t="s">
-        <v>1109</v>
       </c>
       <c r="F400" t="s">
         <v>215</v>
@@ -17817,10 +17815,10 @@
         <v>382</v>
       </c>
       <c r="D401" s="2" t="s">
+        <v>977</v>
+      </c>
+      <c r="E401" s="2" t="s">
         <v>978</v>
-      </c>
-      <c r="E401" s="2" t="s">
-        <v>979</v>
       </c>
       <c r="F401" t="s">
         <v>258</v>
@@ -17852,10 +17850,10 @@
         <v>776</v>
       </c>
       <c r="D402" s="2" t="s">
+        <v>1109</v>
+      </c>
+      <c r="E402" s="2" t="s">
         <v>1110</v>
-      </c>
-      <c r="E402" s="2" t="s">
-        <v>1111</v>
       </c>
       <c r="F402" t="s">
         <v>258</v>
@@ -17887,10 +17885,10 @@
         <v>778</v>
       </c>
       <c r="D403" s="2" t="s">
+        <v>1111</v>
+      </c>
+      <c r="E403" s="2" t="s">
         <v>1112</v>
-      </c>
-      <c r="E403" s="2" t="s">
-        <v>1113</v>
       </c>
       <c r="F403" t="s">
         <v>258</v>
@@ -17922,10 +17920,10 @@
         <v>264</v>
       </c>
       <c r="D404" s="2" t="s">
+        <v>947</v>
+      </c>
+      <c r="E404" s="2" t="s">
         <v>948</v>
-      </c>
-      <c r="E404" s="2" t="s">
-        <v>949</v>
       </c>
       <c r="F404" t="s">
         <v>258</v>
@@ -17957,10 +17955,10 @@
         <v>333</v>
       </c>
       <c r="D405" s="2" t="s">
+        <v>971</v>
+      </c>
+      <c r="E405" s="2" t="s">
         <v>972</v>
-      </c>
-      <c r="E405" s="2" t="s">
-        <v>973</v>
       </c>
       <c r="F405" t="s">
         <v>258</v>
@@ -17992,10 +17990,10 @@
         <v>782</v>
       </c>
       <c r="D406" s="2" t="s">
+        <v>1113</v>
+      </c>
+      <c r="E406" s="2" t="s">
         <v>1114</v>
-      </c>
-      <c r="E406" s="2" t="s">
-        <v>1115</v>
       </c>
       <c r="F406" t="s">
         <v>258</v>
@@ -18027,10 +18025,10 @@
         <v>276</v>
       </c>
       <c r="D407" s="2" t="s">
+        <v>951</v>
+      </c>
+      <c r="E407" s="2" t="s">
         <v>952</v>
-      </c>
-      <c r="E407" s="2" t="s">
-        <v>953</v>
       </c>
       <c r="F407" t="s">
         <v>258</v>
@@ -18062,10 +18060,10 @@
         <v>283</v>
       </c>
       <c r="D408" s="2" t="s">
+        <v>955</v>
+      </c>
+      <c r="E408" s="2" t="s">
         <v>956</v>
-      </c>
-      <c r="E408" s="2" t="s">
-        <v>957</v>
       </c>
       <c r="F408" t="s">
         <v>258</v>
@@ -18097,10 +18095,10 @@
         <v>785</v>
       </c>
       <c r="D409" s="2" t="s">
+        <v>1115</v>
+      </c>
+      <c r="E409" s="2" t="s">
         <v>1116</v>
-      </c>
-      <c r="E409" s="2" t="s">
-        <v>1117</v>
       </c>
       <c r="F409" t="s">
         <v>258</v>
@@ -18132,10 +18130,10 @@
         <v>287</v>
       </c>
       <c r="D410" s="2" t="s">
+        <v>957</v>
+      </c>
+      <c r="E410" s="2" t="s">
         <v>958</v>
-      </c>
-      <c r="E410" s="2" t="s">
-        <v>959</v>
       </c>
       <c r="F410" t="s">
         <v>258</v>
@@ -18167,10 +18165,10 @@
         <v>293</v>
       </c>
       <c r="D411" s="2" t="s">
+        <v>961</v>
+      </c>
+      <c r="E411" s="2" t="s">
         <v>962</v>
-      </c>
-      <c r="E411" s="2" t="s">
-        <v>963</v>
       </c>
       <c r="F411" t="s">
         <v>258</v>
@@ -18202,10 +18200,10 @@
         <v>302</v>
       </c>
       <c r="D412" s="2" t="s">
+        <v>965</v>
+      </c>
+      <c r="E412" s="2" t="s">
         <v>966</v>
-      </c>
-      <c r="E412" s="2" t="s">
-        <v>967</v>
       </c>
       <c r="F412" t="s">
         <v>258</v>
@@ -18237,10 +18235,10 @@
         <v>306</v>
       </c>
       <c r="D413" s="2" t="s">
+        <v>967</v>
+      </c>
+      <c r="E413" s="2" t="s">
         <v>968</v>
-      </c>
-      <c r="E413" s="2" t="s">
-        <v>969</v>
       </c>
       <c r="F413" t="s">
         <v>258</v>
@@ -18272,10 +18270,10 @@
         <v>310</v>
       </c>
       <c r="D414" s="2" t="s">
+        <v>969</v>
+      </c>
+      <c r="E414" s="2" t="s">
         <v>970</v>
-      </c>
-      <c r="E414" s="2" t="s">
-        <v>971</v>
       </c>
       <c r="F414" t="s">
         <v>258</v>
@@ -18307,10 +18305,10 @@
         <v>788</v>
       </c>
       <c r="D415" s="2" t="s">
+        <v>1117</v>
+      </c>
+      <c r="E415" s="2" t="s">
         <v>1118</v>
-      </c>
-      <c r="E415" s="2" t="s">
-        <v>1119</v>
       </c>
       <c r="F415" t="s">
         <v>258</v>
@@ -18342,10 +18340,10 @@
         <v>791</v>
       </c>
       <c r="D416" s="2" t="s">
+        <v>1119</v>
+      </c>
+      <c r="E416" s="2" t="s">
         <v>1120</v>
-      </c>
-      <c r="E416" s="2" t="s">
-        <v>1121</v>
       </c>
       <c r="F416" t="s">
         <v>258</v>
@@ -18377,10 +18375,10 @@
         <v>793</v>
       </c>
       <c r="D417" s="2" t="s">
+        <v>1121</v>
+      </c>
+      <c r="E417" s="2" t="s">
         <v>1122</v>
-      </c>
-      <c r="E417" s="2" t="s">
-        <v>1123</v>
       </c>
       <c r="F417" t="s">
         <v>258</v>
@@ -18412,10 +18410,10 @@
         <v>603</v>
       </c>
       <c r="D418" s="2" t="s">
+        <v>1087</v>
+      </c>
+      <c r="E418" s="2" t="s">
         <v>1088</v>
-      </c>
-      <c r="E418" s="2" t="s">
-        <v>1089</v>
       </c>
       <c r="F418" t="s">
         <v>258</v>

--- a/data/cleaned/dataset_maderas_final.xlsx
+++ b/data/cleaned/dataset_maderas_final.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DATA Y IA\MODULO 1\timber-supply-spanish-naval-industry\data\cleaned\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF89E2A6-E309-413A-BDC6-EE55716C2106}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0943FCC-3BB9-4B03-81C7-004818010A0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1370" yWindow="900" windowWidth="17580" windowHeight="10380" xr2:uid="{F106D049-212B-4983-914F-97B83530BB2C}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{F106D049-212B-4983-914F-97B83530BB2C}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -5851,10 +5851,10 @@
         <v>890</v>
       </c>
       <c r="F59" t="s">
-        <v>59</v>
+        <v>11</v>
       </c>
       <c r="G59" t="s">
-        <v>60</v>
+        <v>143</v>
       </c>
       <c r="H59" t="s">
         <v>13</v>
@@ -14321,7 +14321,7 @@
         <v>950</v>
       </c>
       <c r="F301" t="s">
-        <v>215</v>
+        <v>258</v>
       </c>
       <c r="G301" t="s">
         <v>270</v>
@@ -14356,7 +14356,7 @@
         <v>1096</v>
       </c>
       <c r="F302" t="s">
-        <v>215</v>
+        <v>258</v>
       </c>
       <c r="G302" t="s">
         <v>667</v>
@@ -17086,7 +17086,7 @@
         <v>1098</v>
       </c>
       <c r="F380" t="s">
-        <v>258</v>
+        <v>215</v>
       </c>
       <c r="G380" t="s">
         <v>748</v>
